--- a/ai-agent/output/report.xlsx
+++ b/ai-agent/output/report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="31">
   <si>
     <t>PDF File</t>
   </si>
@@ -96,6 +96,15 @@
   </si>
   <si>
     <t>WP-CF3-CC-2026-002</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>20 June 2026</t>
+  </si>
+  <si>
+    <t>AMF3-CC-2026-004</t>
   </si>
 </sst>
 </file>
@@ -156,14 +165,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="27.484375"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="28.265625"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="13.60546875"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="8.4296875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.13671875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="11.5078125"/>
     <col min="6" max="6" bestFit="true" customWidth="true" width="15.515625"/>
     <col min="7" max="7" bestFit="true" customWidth="true" width="18.18359375"/>
   </cols>
@@ -283,6 +292,167 @@
         <v>27</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>392500.0</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>392500.0</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/ai-agent/output/report.xlsx
+++ b/ai-agent/output/report.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="31">
   <si>
     <t>PDF File</t>
   </si>
@@ -165,7 +165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="27.484375"/>
@@ -453,6 +453,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
